--- a/XLibur.Tests/Resource/Examples/Misc/ShowCase.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/ShowCase.xlsx
@@ -691,10 +691,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.567768" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>

--- a/XLibur.Tests/Resource/Examples/Misc/ShowCase.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/ShowCase.xlsx
@@ -691,11 +691,9 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="9.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="3" width="9.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.424911" style="0" customWidth="1"/>
+    <x:col min="5" max="6" width="10.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">
